--- a/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">Alpha 20.64</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.266</t>
+    <t xml:space="preserve">EA 23.272</t>
   </si>
   <si>
     <t xml:space="preserve">Beta 22.86</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1107">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">Alpha 20.64</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.272</t>
+    <t xml:space="preserve">EA 23.285</t>
   </si>
   <si>
     <t xml:space="preserve">Beta 22.86</t>
@@ -5294,7 +5294,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>798</v>
@@ -5633,7 +5633,7 @@
         <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>806</v>
@@ -9012,7 +9012,7 @@
         <v>560</v>
       </c>
       <c r="B102" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C102" t="s">
         <v>865</v>
@@ -9622,7 +9622,7 @@
         <v>664</v>
       </c>
       <c r="B118" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
         <v>877</v>

--- a/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1107">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"
@@ -137,7 +137,7 @@
   <si>
     <t xml:space="preserve"> *パタパタ*
  * ばさっばさっ*
-*ハタハタ*</t>
+ *ハタハタ*</t>
   </si>
   <si>
     <t xml:space="preserve">"Aaah!"</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">「うみみゃ」
 「みゅー」
 「みゃ」
-*ごろごろ*</t>
+ *ごろごろ*</t>
   </si>
   <si>
     <t xml:space="preserve">「フシューッ」
@@ -2538,7 +2538,7 @@
     <t xml:space="preserve"> *ドスン*
 リトルシスター「見て#bigdaddy、天使がいるわ」
 リトルシスター「急いで#bigdaddy、空で天使が踊っているの！」
-*ドン*</t>
+ *ドン*</t>
   </si>
   <si>
     <t xml:space="preserve">Little Sister: "Kill! Kill!"
@@ -2998,7 +2998,7 @@
   <si>
     <t xml:space="preserve">「あんな極上の女はそうはいねえ」
 「俺の手に掛かれば、どんな女もイチコロよ」
-*レロレロレロ*
+ *レロレロレロ*
 「まったく罪な男に生まれちまったもんだ」</t>
   </si>
   <si>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">Alpha 20.64</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.285</t>
+    <t xml:space="preserve">EA 23.293</t>
   </si>
   <si>
     <t xml:space="preserve">Beta 22.86</t>
@@ -4011,7 +4011,7 @@
 「必须制定充分的计划」
 「好期待未来啊！」
 「偶尔休假也不错」
-「奥尔维纳的葡萄酒是无与伦比的」</t>
+「奥尔维纳的红酒是无与伦比的」</t>
   </si>
   <si>
     <t xml:space="preserve">你感觉被人盯着。
@@ -4222,7 +4222,7 @@
 「不、不要」
 「你这个坏人！」
 「变态！」
-「哇，哇哇」
+「哇、哇哇」
 「为什么打我？」
 「大人就是这个样子」</t>
   </si>
@@ -5294,7 +5294,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C6" t="s">
         <v>798</v>
@@ -5633,7 +5633,7 @@
         <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C14" t="s">
         <v>806</v>
@@ -9012,7 +9012,7 @@
         <v>560</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C102" t="s">
         <v>865</v>
@@ -9622,7 +9622,7 @@
         <v>664</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>758</v>
       </c>
       <c r="C118" t="s">
         <v>877</v>

--- a/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/CharaText.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="1107">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">artist</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">"You senseless bastard!"
@@ -137,7 +137,7 @@
   <si>
     <t xml:space="preserve"> *パタパタ*
  * ばさっばさっ*
- *ハタハタ*</t>
+*ハタハタ*</t>
   </si>
   <si>
     <t xml:space="preserve">"Aaah!"</t>
@@ -430,7 +430,7 @@
     <t xml:space="preserve">「うみみゃ」
 「みゅー」
 「みゃ」
- *ごろごろ*</t>
+*ごろごろ*</t>
   </si>
   <si>
     <t xml:space="preserve">「フシューッ」
@@ -2538,7 +2538,7 @@
     <t xml:space="preserve"> *ドスン*
 リトルシスター「見て#bigdaddy、天使がいるわ」
 リトルシスター「急いで#bigdaddy、空で天使が踊っているの！」
- *ドン*</t>
+*ドン*</t>
   </si>
   <si>
     <t xml:space="preserve">Little Sister: "Kill! Kill!"
@@ -2998,7 +2998,7 @@
   <si>
     <t xml:space="preserve">「あんな極上の女はそうはいねえ」
 「俺の手に掛かれば、どんな女もイチコロよ」
- *レロレロレロ*
+*レロレロレロ*
 「まったく罪な男に生まれちまったもんだ」</t>
   </si>
   <si>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">Alpha 20.64</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.293</t>
+    <t xml:space="preserve">EA 23.285</t>
   </si>
   <si>
     <t xml:space="preserve">Beta 22.86</t>
@@ -4011,7 +4011,7 @@
 「必须制定充分的计划」
 「好期待未来啊！」
 「偶尔休假也不错」
-「奥尔维纳的红酒是无与伦比的」</t>
+「奥尔维纳的葡萄酒是无与伦比的」</t>
   </si>
   <si>
     <t xml:space="preserve">你感觉被人盯着。
@@ -4222,7 +4222,7 @@
 「不、不要」
 「你这个坏人！」
 「变态！」
-「哇、哇哇」
+「哇，哇哇」
 「为什么打我？」
 「大人就是这个样子」</t>
   </si>
@@ -5294,7 +5294,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>798</v>
@@ -5633,7 +5633,7 @@
         <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>806</v>
@@ -9012,7 +9012,7 @@
         <v>560</v>
       </c>
       <c r="B102" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C102" t="s">
         <v>865</v>
@@ -9622,7 +9622,7 @@
         <v>664</v>
       </c>
       <c r="B118" t="s">
-        <v>758</v>
+        <v>18</v>
       </c>
       <c r="C118" t="s">
         <v>877</v>
